--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -20024,16 +20024,16 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20674</v>
+        <v>20681</v>
       </c>
       <c r="O114" t="n">
-        <v>20674</v>
+        <v>20681</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>75.93171155675213</v>
+        <v>75.95742123948878</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21308,16 +21308,16 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>7554</v>
+        <v>9010</v>
       </c>
       <c r="O122" t="n">
-        <v>7554</v>
+        <v>9010</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>27.74442048465249</v>
+        <v>33.09203449387331</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5072948</v>
+        <v>5074411</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -18592,16 +18592,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>10710</v>
+        <v>10713</v>
       </c>
       <c r="O105" t="n">
-        <v>10710</v>
+        <v>10713</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>39.33581458705695</v>
+        <v>39.34683302251551</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20024,16 +20024,16 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20681</v>
+        <v>20689</v>
       </c>
       <c r="O114" t="n">
-        <v>20681</v>
+        <v>20689</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>75.95742123948878</v>
+        <v>75.98680373404493</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21308,16 +21308,16 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>9010</v>
+        <v>10905</v>
       </c>
       <c r="O122" t="n">
-        <v>9010</v>
+        <v>10905</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>33.09203449387331</v>
+        <v>40.05201289186331</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5074411</v>
+        <v>5076317</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -18592,16 +18592,16 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>10713</v>
+        <v>10714</v>
       </c>
       <c r="O105" t="n">
-        <v>10713</v>
+        <v>10714</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>39.34683302251551</v>
+        <v>39.35050583433503</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -21308,16 +21308,16 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>10905</v>
+        <v>12707</v>
       </c>
       <c r="O122" t="n">
-        <v>10905</v>
+        <v>12707</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>40.05201289186331</v>
+        <v>46.67041979063797</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21782,6 +21782,154 @@
       <c r="BC124" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1384</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1384</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1.13046283607102</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21818,7 +21966,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -21901,7 +22049,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -21911,7 +22059,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -21963,7 +22111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5076317</v>
+        <v>5079504</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>10018</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>111.2147497090854</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>4369</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>77.71617267505417</v>
       </c>
@@ -1756,9 +1750,6 @@
       <c r="P8" t="n">
         <v>22</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>5.468161628915639</v>
       </c>
@@ -2464,9 +2455,6 @@
       <c r="P12" t="n">
         <v>12</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>2.982633615772166</v>
       </c>
@@ -3172,9 +3160,6 @@
       <c r="P16" t="n">
         <v>9</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>2.236975211829125</v>
       </c>
@@ -3880,9 +3865,6 @@
       <c r="P20" t="n">
         <v>11</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -4585,9 +4567,6 @@
       <c r="O24" t="n">
         <v>2762</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>30.66232169060629</v>
       </c>
@@ -4881,9 +4860,6 @@
       <c r="O26" t="n">
         <v>5279</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>93.90333612991782</v>
       </c>
@@ -5428,9 +5404,6 @@
       <c r="P29" t="n">
         <v>15</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>3.728292019715209</v>
       </c>
@@ -6136,9 +6109,6 @@
       <c r="P33" t="n">
         <v>11</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -6844,9 +6814,6 @@
       <c r="P37" t="n">
         <v>14</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>3.479739218400861</v>
       </c>
@@ -7552,9 +7519,6 @@
       <c r="P41" t="n">
         <v>19</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>4.722503224972597</v>
       </c>
@@ -8257,9 +8221,6 @@
       <c r="O45" t="n">
         <v>393</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>4.362886467924791</v>
       </c>
@@ -8553,9 +8514,6 @@
       <c r="O47" t="n">
         <v>1571</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>27.9450920742756</v>
       </c>
@@ -9100,9 +9058,6 @@
       <c r="P50" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.73986960920043</v>
       </c>
@@ -9657,9 +9612,6 @@
       <c r="O53" t="n">
         <v>103</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>1.143453705333978</v>
       </c>
@@ -9808,9 +9760,6 @@
       <c r="P54" t="n">
         <v>13</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>3.231186417086514</v>
       </c>
@@ -10365,9 +10314,6 @@
       <c r="O57" t="n">
         <v>67</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.7437999830813258</v>
       </c>
@@ -10516,9 +10462,6 @@
       <c r="P58" t="n">
         <v>20</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>4.971056026286944</v>
       </c>
@@ -11073,9 +11016,6 @@
       <c r="O61" t="n">
         <v>50</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.5550746142397954</v>
       </c>
@@ -11224,9 +11164,6 @@
       <c r="P62" t="n">
         <v>11</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>2.734080814457819</v>
       </c>
@@ -11781,9 +11718,6 @@
       <c r="O65" t="n">
         <v>52</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.5772775988093871</v>
       </c>
@@ -11932,9 +11866,6 @@
       <c r="P66" t="n">
         <v>21</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>5.219608827601292</v>
       </c>
@@ -12341,9 +12272,6 @@
       <c r="O68" t="n">
         <v>3815</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>14.011777091468</v>
       </c>
@@ -12489,9 +12417,6 @@
       <c r="O69" t="n">
         <v>98</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>1.087946243909999</v>
       </c>
@@ -12785,9 +12710,6 @@
       <c r="O71" t="n">
         <v>264</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>4.696056211081323</v>
       </c>
@@ -13329,9 +13251,6 @@
       <c r="O74" t="n">
         <v>27</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.2997402916894895</v>
       </c>
@@ -13480,9 +13399,6 @@
       <c r="P75" t="n">
         <v>26</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>6.462372834173028</v>
       </c>
@@ -14037,9 +13953,6 @@
       <c r="O78" t="n">
         <v>22</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.2442328302655099</v>
       </c>
@@ -14188,9 +14101,6 @@
       <c r="P79" t="n">
         <v>8</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>1.988422410514778</v>
       </c>
@@ -14745,9 +14655,6 @@
       <c r="O82" t="n">
         <v>14</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -14896,9 +14803,6 @@
       <c r="P83" t="n">
         <v>3</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -15453,9 +15357,6 @@
       <c r="O86" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -15604,9 +15505,6 @@
       <c r="P87" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.4971056026286944</v>
       </c>
@@ -16013,9 +15911,6 @@
       <c r="O89" t="n">
         <v>4148</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>15.23482342736809</v>
       </c>
@@ -16161,9 +16056,6 @@
       <c r="O90" t="n">
         <v>42</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.4662626759614281</v>
       </c>
@@ -16457,9 +16349,6 @@
       <c r="O92" t="n">
         <v>93</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.654292528903648</v>
       </c>
@@ -17001,9 +16890,6 @@
       <c r="O95" t="n">
         <v>11</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -17152,9 +17038,6 @@
       <c r="P96" t="n">
         <v>5</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>1.242764006571736</v>
       </c>
@@ -17709,9 +17592,6 @@
       <c r="O99" t="n">
         <v>10</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -18005,9 +17885,6 @@
       <c r="O101" t="n">
         <v>11</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -18301,9 +18178,6 @@
       <c r="O103" t="n">
         <v>7</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -18597,9 +18471,6 @@
       <c r="O105" t="n">
         <v>10714</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>39.35050583433503</v>
       </c>
@@ -18745,9 +18616,6 @@
       <c r="O106" t="n">
         <v>37</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.4107552145374486</v>
       </c>
@@ -19041,9 +18909,6 @@
       <c r="O108" t="n">
         <v>50</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.8894045854320688</v>
       </c>
@@ -19437,9 +19302,6 @@
       <c r="O110" t="n">
         <v>261</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.213186994374665</v>
       </c>
@@ -19585,9 +19447,6 @@
       <c r="O111" t="n">
         <v>239</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.1952172094082182</v>
       </c>
@@ -19733,9 +19592,6 @@
       <c r="O112" t="n">
         <v>272</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.2221718868578884</v>
       </c>
@@ -19881,9 +19737,6 @@
       <c r="O113" t="n">
         <v>251</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.2050189102990073</v>
       </c>
@@ -20029,9 +19882,6 @@
       <c r="O114" t="n">
         <v>20689</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>75.98680373404493</v>
       </c>
@@ -20177,9 +20027,6 @@
       <c r="O115" t="n">
         <v>6</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -20573,9 +20420,6 @@
       <c r="O117" t="n">
         <v>310</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.2532106063453876</v>
       </c>
@@ -20721,9 +20565,6 @@
       <c r="O118" t="n">
         <v>446</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.3642965497743318</v>
       </c>
@@ -20869,9 +20710,6 @@
       <c r="O119" t="n">
         <v>486</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.3969688860769625</v>
       </c>
@@ -21017,9 +20855,6 @@
       <c r="O120" t="n">
         <v>749</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.6117894972667589</v>
       </c>
@@ -21165,9 +21000,6 @@
       <c r="O121" t="n">
         <v>886</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.7236922491032689</v>
       </c>
@@ -21313,9 +21145,6 @@
       <c r="O122" t="n">
         <v>12707</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>46.67041979063797</v>
       </c>
@@ -21456,16 +21285,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R123" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21618,10 +21444,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -21856,9 +21682,6 @@
       </c>
       <c r="O125" t="n">
         <v>1384</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>1.13046283607102</v>
@@ -22111,7 +21934,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5079504</v>
+        <v>5079505</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19983,12 +19983,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20022,95 +20022,81 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="R115" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.4107552145374486</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20123,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -20186,98 +20172,23 @@
       <c r="O116" t="n">
         <v>6</v>
       </c>
+      <c r="R116" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -20371,17 +20282,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20406,7 +20317,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20415,81 +20326,170 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>310</v>
+        <v>6</v>
       </c>
       <c r="O117" t="n">
-        <v>310</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.2532106063453876</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20551,7 +20551,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20560,13 +20560,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="O118" t="n">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="R118" t="n">
-        <v>0.3642965497743318</v>
+        <v>0.2532106063453876</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -20705,13 +20705,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="O119" t="n">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="R119" t="n">
-        <v>0.3969688860769625</v>
+        <v>0.3642965497743318</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -20850,13 +20850,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>749</v>
+        <v>486</v>
       </c>
       <c r="O120" t="n">
-        <v>749</v>
+        <v>486</v>
       </c>
       <c r="R120" t="n">
-        <v>0.6117894972667589</v>
+        <v>0.3969688860769625</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>886</v>
+        <v>749</v>
       </c>
       <c r="O121" t="n">
-        <v>886</v>
+        <v>749</v>
       </c>
       <c r="R121" t="n">
-        <v>0.7236922491032689</v>
+        <v>0.6117894972667589</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>12707</v>
+        <v>886</v>
       </c>
       <c r="O122" t="n">
-        <v>12707</v>
+        <v>886</v>
       </c>
       <c r="R122" t="n">
-        <v>46.67041979063797</v>
+        <v>0.7236922491032689</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21179,42 +21179,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21246,12 +21246,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21285,95 +21285,81 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>12707</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>12707</v>
       </c>
       <c r="R123" t="n">
-        <v>0.05336427512592412</v>
+        <v>46.67041979063797</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21400,7 +21386,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -21449,98 +21435,23 @@
       <c r="O124" t="n">
         <v>3</v>
       </c>
+      <c r="R124" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -21634,123 +21545,357 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>D038</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>流行性感冒</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N125" t="n">
+      <c r="N126" t="n">
         <v>1384</v>
       </c>
-      <c r="O125" t="n">
+      <c r="O126" t="n">
         <v>1384</v>
       </c>
-      <c r="R125" t="n">
+      <c r="R126" t="n">
         <v>1.13046283607102</v>
       </c>
-      <c r="S125" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO125" t="inlineStr">
+      <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP125" t="inlineStr">
+      <c r="AP126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR125" t="inlineStr">
+      <c r="AR126" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS125" t="inlineStr"/>
-      <c r="AT125" t="n">
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
         <v>0</v>
       </c>
-      <c r="AU125" t="inlineStr">
+      <c r="AU126" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV125" t="inlineStr">
+      <c r="AV126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW125" t="inlineStr">
+      <c r="AW126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX125" t="inlineStr">
+      <c r="AX126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY125" t="inlineStr">
+      <c r="AY126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ125" t="inlineStr">
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA125" t="inlineStr">
+      <c r="BA126" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB125" t="inlineStr">
+      <c r="BB126" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC125" t="inlineStr">
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21872,7 +22017,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -21882,7 +22027,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -21934,7 +22079,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5079505</v>
+        <v>5079542</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20689</v>
+        <v>20695</v>
       </c>
       <c r="O114" t="n">
-        <v>20689</v>
+        <v>20695</v>
       </c>
       <c r="R114" t="n">
-        <v>75.98680373404493</v>
+        <v>76.00884060496206</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21285,13 +21285,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>12707</v>
+        <v>17223</v>
       </c>
       <c r="O123" t="n">
-        <v>12707</v>
+        <v>17223</v>
       </c>
       <c r="R123" t="n">
-        <v>46.67041979063797</v>
+        <v>63.25683796758935</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5079542</v>
+        <v>5084064</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20695</v>
+        <v>20696</v>
       </c>
       <c r="O114" t="n">
-        <v>20695</v>
+        <v>20696</v>
       </c>
       <c r="R114" t="n">
-        <v>76.00884060496206</v>
+        <v>76.01251341678159</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21285,13 +21285,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>17223</v>
+        <v>19881</v>
       </c>
       <c r="O123" t="n">
-        <v>17223</v>
+        <v>19881</v>
       </c>
       <c r="R123" t="n">
-        <v>63.25683796758935</v>
+        <v>73.01917178387295</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5084064</v>
+        <v>5086723</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20696</v>
+        <v>20697</v>
       </c>
       <c r="O114" t="n">
-        <v>20696</v>
+        <v>20697</v>
       </c>
       <c r="R114" t="n">
-        <v>76.01251341678159</v>
+        <v>76.0161862286011</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21285,13 +21285,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>19881</v>
+        <v>22354</v>
       </c>
       <c r="O123" t="n">
-        <v>19881</v>
+        <v>22354</v>
       </c>
       <c r="R123" t="n">
-        <v>73.01917178387295</v>
+        <v>82.10203541354539</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21896,6 +21896,151 @@
         </is>
       </c>
       <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1926</v>
+      </c>
+      <c r="O127" t="n">
+        <v>1926</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.573172992971666</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21934,7 +22079,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22162,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -22027,7 +22172,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -22079,7 +22224,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5086723</v>
+        <v>5091123</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -20128,12 +20128,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20167,95 +20167,84 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>969125</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>969125</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>0.1067285502518482</v>
+        <v>68.59051147468263</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20271,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -20331,98 +20320,23 @@
       <c r="O117" t="n">
         <v>6</v>
       </c>
+      <c r="R117" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -20516,17 +20430,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20551,7 +20465,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20560,81 +20474,170 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>310</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>310</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.2532106063453876</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20696,7 +20699,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -20705,13 +20708,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="O119" t="n">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="R119" t="n">
-        <v>0.3642965497743318</v>
+        <v>0.2532106063453876</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20841,7 +20844,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -20850,13 +20853,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="O120" t="n">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="R120" t="n">
-        <v>0.3969688860769625</v>
+        <v>0.3642965497743318</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20986,7 +20989,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20995,13 +20998,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>749</v>
+        <v>486</v>
       </c>
       <c r="O121" t="n">
-        <v>749</v>
+        <v>486</v>
       </c>
       <c r="R121" t="n">
-        <v>0.6117894972667589</v>
+        <v>0.3969688860769625</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21131,7 +21134,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21140,13 +21143,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>886</v>
+        <v>749</v>
       </c>
       <c r="O122" t="n">
-        <v>886</v>
+        <v>749</v>
       </c>
       <c r="R122" t="n">
-        <v>0.7236922491032689</v>
+        <v>0.6117894972667589</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21246,12 +21249,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21276,22 +21279,22 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>22354</v>
+        <v>886</v>
       </c>
       <c r="O123" t="n">
-        <v>22354</v>
+        <v>886</v>
       </c>
       <c r="R123" t="n">
-        <v>82.10203541354539</v>
+        <v>0.7236922491032689</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21324,42 +21327,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21391,12 +21394,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21430,95 +21433,81 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>3</v>
+        <v>22354</v>
       </c>
       <c r="O124" t="n">
-        <v>3</v>
+        <v>22354</v>
       </c>
       <c r="R124" t="n">
-        <v>0.05336427512592412</v>
+        <v>82.10203541354539</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21545,7 +21534,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -21589,103 +21578,28 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O125" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -21779,17 +21693,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21814,7 +21728,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21823,81 +21737,170 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1384</v>
+        <v>8</v>
       </c>
       <c r="O126" t="n">
-        <v>1384</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1.13046283607102</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21962,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21968,13 +21971,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="O127" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="R127" t="n">
-        <v>1.573172992971666</v>
+        <v>1.13046283607102</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22041,6 +22044,151 @@
         </is>
       </c>
       <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1926</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1926</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.573172992971666</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22162,7 +22310,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -22172,7 +22320,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -22224,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5091123</v>
+        <v>6060253</v>
       </c>
     </row>
     <row r="16">
@@ -22234,7 +22382,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20697</v>
+        <v>20706</v>
       </c>
       <c r="O114" t="n">
-        <v>20697</v>
+        <v>20706</v>
       </c>
       <c r="R114" t="n">
-        <v>76.0161862286011</v>
+        <v>76.04924153497679</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>22354</v>
+        <v>27389</v>
       </c>
       <c r="O124" t="n">
-        <v>22354</v>
+        <v>27389</v>
       </c>
       <c r="R124" t="n">
-        <v>82.10203541354539</v>
+        <v>100.5946429248275</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21578,13 +21578,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R125" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21737,10 +21737,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6060253</v>
+        <v>6065299</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>27389</v>
+        <v>29584</v>
       </c>
       <c r="O124" t="n">
-        <v>27389</v>
+        <v>29584</v>
       </c>
       <c r="R124" t="n">
-        <v>100.5946429248275</v>
+        <v>108.6564648686735</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6065299</v>
+        <v>6067494</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>29584</v>
+        <v>30721</v>
       </c>
       <c r="O124" t="n">
-        <v>29584</v>
+        <v>30721</v>
       </c>
       <c r="R124" t="n">
-        <v>108.6564648686735</v>
+        <v>112.8324519074675</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21578,13 +21578,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O125" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R125" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21737,10 +21737,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O126" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6067494</v>
+        <v>6068633</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>30721</v>
+        <v>31541</v>
       </c>
       <c r="O124" t="n">
-        <v>30721</v>
+        <v>31541</v>
       </c>
       <c r="R124" t="n">
-        <v>112.8324519074675</v>
+        <v>115.8441575994737</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6068633</v>
+        <v>6069453</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>31541</v>
+        <v>33725</v>
       </c>
       <c r="O124" t="n">
-        <v>31541</v>
+        <v>33725</v>
       </c>
       <c r="R124" t="n">
-        <v>115.8441575994737</v>
+        <v>123.8655786133049</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6069453</v>
+        <v>6071637</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>33725</v>
+        <v>39623</v>
       </c>
       <c r="O124" t="n">
-        <v>33725</v>
+        <v>39623</v>
       </c>
       <c r="R124" t="n">
-        <v>123.8655786133049</v>
+        <v>145.5278227248326</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21578,13 +21578,13 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O125" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R125" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
@@ -21737,10 +21737,10 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O126" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -22189,6 +22189,151 @@
         </is>
       </c>
       <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>2417</v>
+      </c>
+      <c r="O129" t="n">
+        <v>2417</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1.974225921086457</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22227,7 +22372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -22310,7 +22455,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -22320,7 +22465,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -22372,7 +22517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6071637</v>
+        <v>6079954</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20706</v>
+        <v>20709</v>
       </c>
       <c r="O114" t="n">
-        <v>20706</v>
+        <v>20709</v>
       </c>
       <c r="R114" t="n">
-        <v>76.04924153497679</v>
+        <v>76.06025997043533</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>39623</v>
+        <v>42201</v>
       </c>
       <c r="O124" t="n">
-        <v>39623</v>
+        <v>42201</v>
       </c>
       <c r="R124" t="n">
-        <v>145.5278227248326</v>
+        <v>154.9963315955547</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6079954</v>
+        <v>6082535</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20709</v>
+        <v>20711</v>
       </c>
       <c r="O114" t="n">
-        <v>20709</v>
+        <v>20711</v>
       </c>
       <c r="R114" t="n">
-        <v>76.06025997043533</v>
+        <v>76.06760559407438</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>42201</v>
+        <v>44529</v>
       </c>
       <c r="O124" t="n">
-        <v>42201</v>
+        <v>44529</v>
       </c>
       <c r="R124" t="n">
-        <v>154.9963315955547</v>
+        <v>163.5466375113967</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6082535</v>
+        <v>6084865</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21433,13 +21433,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>44529</v>
+        <v>45653</v>
       </c>
       <c r="O124" t="n">
-        <v>44529</v>
+        <v>45653</v>
       </c>
       <c r="R124" t="n">
-        <v>163.5466375113967</v>
+        <v>167.674877996537</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6084865</v>
+        <v>6085989</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -18572,12 +18572,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18611,17 +18611,14 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O106" t="n">
-        <v>37</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0.4107552145374486</v>
+        <v>40</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -18650,42 +18647,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18717,12 +18714,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18756,20 +18753,14 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>592906</v>
+        <v>7331</v>
       </c>
       <c r="O107" t="n">
-        <v>592906</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" t="n">
-        <v>41.96334404375925</v>
+        <v>7331</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -18798,42 +18789,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18865,12 +18856,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18904,95 +18895,78 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="O108" t="n">
-        <v>50</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0.8894045854320688</v>
+        <v>28</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19019,17 +18993,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19063,170 +19037,78 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>50</v>
+        <v>1064</v>
       </c>
       <c r="O109" t="n">
-        <v>50</v>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
+        <v>1064</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP109" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AT109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV109" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19258,12 +19140,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19288,7 +19170,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19297,17 +19179,14 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="O110" t="n">
-        <v>261</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.213186994374665</v>
+        <v>188</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -19336,42 +19215,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19403,12 +19282,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19433,7 +19312,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19442,17 +19321,14 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>239</v>
+        <v>37</v>
       </c>
       <c r="O111" t="n">
-        <v>239</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.1952172094082182</v>
+        <v>37</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -19481,42 +19357,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19548,12 +19424,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19578,7 +19454,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19587,17 +19463,14 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>272</v>
+        <v>814</v>
       </c>
       <c r="O112" t="n">
-        <v>272</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0.2221718868578884</v>
+        <v>814</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -19626,42 +19499,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19693,12 +19566,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -19723,7 +19596,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -19732,17 +19605,14 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>251</v>
+        <v>1213</v>
       </c>
       <c r="O113" t="n">
-        <v>251</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0.2050189102990073</v>
+        <v>1213</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -19771,42 +19641,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19838,12 +19708,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19868,22 +19738,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>20711</v>
+        <v>37</v>
       </c>
       <c r="O114" t="n">
-        <v>20711</v>
+        <v>37</v>
       </c>
       <c r="R114" t="n">
-        <v>76.06760559407438</v>
+        <v>0.4107552145374486</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -19916,42 +19786,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -19983,12 +19853,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20013,22 +19883,25 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>37</v>
+        <v>592906</v>
       </c>
       <c r="O115" t="n">
-        <v>37</v>
+        <v>592906</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>0.4107552145374486</v>
+        <v>41.96334404375925</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20061,42 +19934,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20128,12 +20001,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20158,93 +20031,104 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>969125</v>
+        <v>50</v>
       </c>
       <c r="O116" t="n">
-        <v>969125</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="R116" t="n">
-        <v>68.59051147468263</v>
+        <v>0.8894045854320688</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20271,7 +20155,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -20306,37 +20190,112 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.1067285502518482</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -20430,17 +20389,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20465,179 +20424,90 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>261</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
+        <v>261</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.213186994374665</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20699,22 +20569,22 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="O119" t="n">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="R119" t="n">
-        <v>0.2532106063453876</v>
+        <v>0.1952172094082182</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -20844,22 +20714,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>446</v>
+        <v>272</v>
       </c>
       <c r="O120" t="n">
-        <v>446</v>
+        <v>272</v>
       </c>
       <c r="R120" t="n">
-        <v>0.3642965497743318</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20989,22 +20859,22 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>486</v>
+        <v>251</v>
       </c>
       <c r="O121" t="n">
-        <v>486</v>
+        <v>251</v>
       </c>
       <c r="R121" t="n">
-        <v>0.3969688860769625</v>
+        <v>0.2050189102990073</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21104,12 +20974,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21134,7 +21004,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21143,13 +21013,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>749</v>
+        <v>20712</v>
       </c>
       <c r="O122" t="n">
-        <v>749</v>
+        <v>20712</v>
       </c>
       <c r="R122" t="n">
-        <v>0.6117894972667589</v>
+        <v>76.07127840589389</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21182,42 +21052,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21249,12 +21119,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21279,7 +21149,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -21288,17 +21158,14 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>886</v>
+        <v>248</v>
       </c>
       <c r="O123" t="n">
-        <v>886</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0.7236922491032689</v>
+        <v>248</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -21327,42 +21194,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21394,12 +21261,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21424,26 +21291,23 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>45653</v>
+        <v>13031</v>
       </c>
       <c r="O124" t="n">
-        <v>45653</v>
-      </c>
-      <c r="R124" t="n">
-        <v>167.674877996537</v>
+        <v>13031</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -21477,12 +21341,12 @@
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -21497,12 +21361,12 @@
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
@@ -21539,12 +21403,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21569,104 +21433,87 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="O125" t="n">
-        <v>14</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.2490332839209793</v>
+        <v>48</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21693,17 +21540,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21728,179 +21575,87 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>14</v>
+        <v>2254</v>
       </c>
       <c r="O126" t="n">
-        <v>14</v>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
+        <v>2254</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV126" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21932,12 +21687,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21962,26 +21717,23 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1384</v>
+        <v>578</v>
       </c>
       <c r="O127" t="n">
-        <v>1384</v>
-      </c>
-      <c r="R127" t="n">
-        <v>1.13046283607102</v>
+        <v>578</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -22010,42 +21762,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22077,12 +21829,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22107,26 +21859,23 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>1926</v>
+        <v>91</v>
       </c>
       <c r="O128" t="n">
-        <v>1926</v>
-      </c>
-      <c r="R128" t="n">
-        <v>1.573172992971666</v>
+        <v>91</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -22155,42 +21904,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22222,12 +21971,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22252,26 +22001,23 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2417</v>
+        <v>2150</v>
       </c>
       <c r="O129" t="n">
-        <v>2417</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1.974225921086457</v>
+        <v>2150</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -22300,42 +22046,4387 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>2311</v>
+      </c>
+      <c r="O130" t="n">
+        <v>2311</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>38</v>
+      </c>
+      <c r="O131" t="n">
+        <v>38</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.4218567068222445</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>969125</v>
+      </c>
+      <c r="O132" t="n">
+        <v>969125</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3</v>
+      </c>
+      <c r="R132" t="n">
+        <v>68.59051147468263</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>6</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>6</v>
+      </c>
+      <c r="O134" t="n">
+        <v>6</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>310</v>
+      </c>
+      <c r="O135" t="n">
+        <v>310</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.2532106063453876</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW129" t="inlineStr">
+      <c r="AW135" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX129" t="inlineStr">
+      <c r="AX135" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY129" t="inlineStr">
+      <c r="AY135" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ129" t="inlineStr">
+      <c r="AZ135" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA129" t="inlineStr">
+      <c r="BA135" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB129" t="inlineStr">
+      <c r="BB135" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC129" t="inlineStr">
+      <c r="BC135" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>446</v>
+      </c>
+      <c r="O136" t="n">
+        <v>446</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3642965497743318</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>486</v>
+      </c>
+      <c r="O137" t="n">
+        <v>486</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3969688860769625</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>749</v>
+      </c>
+      <c r="O138" t="n">
+        <v>749</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6117894972667589</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>886</v>
+      </c>
+      <c r="O139" t="n">
+        <v>886</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.7236922491032689</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>52248</v>
+      </c>
+      <c r="O140" t="n">
+        <v>52248</v>
+      </c>
+      <c r="R140" t="n">
+        <v>191.89707194627</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>1195</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1195</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>25148</v>
+      </c>
+      <c r="O142" t="n">
+        <v>25148</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>117</v>
+      </c>
+      <c r="O143" t="n">
+        <v>117</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>7898</v>
+      </c>
+      <c r="O144" t="n">
+        <v>7898</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1898</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1898</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>319</v>
+      </c>
+      <c r="O146" t="n">
+        <v>319</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>7485</v>
+      </c>
+      <c r="O147" t="n">
+        <v>7485</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>2385</v>
+      </c>
+      <c r="O148" t="n">
+        <v>2385</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>24</v>
+      </c>
+      <c r="O149" t="n">
+        <v>24</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.426914201007393</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>24</v>
+      </c>
+      <c r="O150" t="n">
+        <v>24</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1384</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1384</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1.13046283607102</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>1926</v>
+      </c>
+      <c r="O152" t="n">
+        <v>1926</v>
+      </c>
+      <c r="R152" t="n">
+        <v>1.573172992971666</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>2417</v>
+      </c>
+      <c r="O153" t="n">
+        <v>2417</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1.974225921086457</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>4094</v>
+      </c>
+      <c r="O154" t="n">
+        <v>4094</v>
+      </c>
+      <c r="R154" t="n">
+        <v>3.344013620574247</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>3017</v>
+      </c>
+      <c r="O155" t="n">
+        <v>3017</v>
+      </c>
+      <c r="R155" t="n">
+        <v>11.08087325949121</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="n">
+        <v>2</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="n">
+        <v>2</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22372,7 +26463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -22455,7 +26546,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -22465,7 +26556,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -22485,7 +26576,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -22517,7 +26608,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6085989</v>
+        <v>6177580</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21013,13 +21013,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>20712</v>
+        <v>20715</v>
       </c>
       <c r="O122" t="n">
-        <v>20712</v>
+        <v>20715</v>
       </c>
       <c r="R122" t="n">
-        <v>76.07127840589389</v>
+        <v>76.08229684135244</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52248</v>
+        <v>52331</v>
       </c>
       <c r="O140" t="n">
-        <v>52248</v>
+        <v>52331</v>
       </c>
       <c r="R140" t="n">
-        <v>191.89707194627</v>
+        <v>192.2019153272902</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -25959,13 +25959,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>3017</v>
+        <v>5573</v>
       </c>
       <c r="O155" t="n">
-        <v>3017</v>
+        <v>5573</v>
       </c>
       <c r="R155" t="n">
-        <v>11.08087325949121</v>
+        <v>20.46858027018379</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26104,13 +26104,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26263,10 +26263,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6177580</v>
+        <v>6180223</v>
       </c>
     </row>
     <row r="16">
